--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_reset_cost_v8【迷宫-能力-刷新次数与消耗】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_reset_cost_v8【迷宫-能力-刷新次数与消耗】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D357DF-E9E8-420F-823E-03D9BE1E851A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42030132-9B54-4B83-AFE1-85B50508AB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,19 +86,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46200001:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46200001:5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46200001:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46200001:5000</t>
+    <t>46900001:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900001:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900001:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46900001:50000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +490,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_reset_cost_v8【迷宫-能力-刷新次数与消耗】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_reset_cost_v8【迷宫-能力-刷新次数与消耗】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42030132-9B54-4B83-AFE1-85B50508AB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D357DF-E9E8-420F-823E-03D9BE1E851A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,19 +86,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>46900001:50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46900001:500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46900001:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>46900001:50000</t>
+    <t>46200001:50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46200001:5000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +490,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
